--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105166439</v>
+        <v>105166467</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601257.9826317879</v>
+        <v>601342</v>
       </c>
       <c r="R2" t="n">
-        <v>7035787.513988073</v>
+        <v>7035937</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,24 +743,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett trettiotal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105166451</v>
+        <v>105166448</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601304.2086765055</v>
+        <v>601307</v>
       </c>
       <c r="R3" t="n">
-        <v>7035772.407395232</v>
+        <v>7035771</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +844,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +880,7 @@
         <v>105166442</v>
       </c>
       <c r="B4" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601314.574610556</v>
+        <v>601315</v>
       </c>
       <c r="R4" t="n">
-        <v>7035728.39387867</v>
+        <v>7035729</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +945,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105166454</v>
+        <v>105166473</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601301.8690936328</v>
+        <v>601383</v>
       </c>
       <c r="R5" t="n">
-        <v>7035775.468490278</v>
+        <v>7036003</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,19 +1046,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105166445</v>
+        <v>105166457</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601317.4839516783</v>
+        <v>601301</v>
       </c>
       <c r="R6" t="n">
-        <v>7035735.652617416</v>
+        <v>7035773</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,27 +1147,18 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105166448</v>
+        <v>105166462</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601306.9395558182</v>
+        <v>601281</v>
       </c>
       <c r="R7" t="n">
-        <v>7035771.15030306</v>
+        <v>7035861</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,19 +1249,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105166429</v>
+        <v>105166465</v>
       </c>
       <c r="B8" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601387.0193692304</v>
+        <v>601338</v>
       </c>
       <c r="R8" t="n">
-        <v>7035763.389192169</v>
+        <v>7035915</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,19 +1350,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,37 +1383,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105166460</v>
+        <v>105166445</v>
       </c>
       <c r="B9" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601299.053086695</v>
+        <v>601318</v>
       </c>
       <c r="R9" t="n">
-        <v>7035779.410271019</v>
+        <v>7035735</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1565,19 +1451,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,37 +1484,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105166457</v>
+        <v>105166454</v>
       </c>
       <c r="B10" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5321</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601301.0439371982</v>
+        <v>601302</v>
       </c>
       <c r="R10" t="n">
-        <v>7035773.20283249</v>
+        <v>7035775</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,28 +1552,17 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1718,6 +1578,516 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105166469</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>601360</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7035964</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105166460</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>601299</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7035779</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105166451</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>601304</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7035772</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105166429</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601387</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7035763</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105166439</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601258</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7035788</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett trettiotal</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166467</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166473</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166457</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166465</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166445</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166454</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166460</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166451</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166429</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2092,8 +2162,29 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166439</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105166467</v>
+        <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601342</v>
+        <v>601417</v>
       </c>
       <c r="R2" t="n">
-        <v>7035937</v>
+        <v>7035853</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166467</t>
+          <t>https://artportalen.se/Sighting/135978189</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105166448</v>
+        <v>105166467</v>
       </c>
       <c r="B3" t="n">
-        <v>92208</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601307</v>
+        <v>601342</v>
       </c>
       <c r="R3" t="n">
-        <v>7035771</v>
+        <v>7035937</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,16 +882,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166448</t>
+          <t>https://artportalen.se/Sighting/105166467</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105166442</v>
+        <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>81312</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +899,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601315</v>
+        <v>601328</v>
       </c>
       <c r="R4" t="n">
-        <v>7035729</v>
+        <v>7035847</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,31 +973,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166442</t>
+          <t>https://artportalen.se/Sighting/135978184</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105166473</v>
+        <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>92369</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +1001,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601383</v>
+        <v>601426</v>
       </c>
       <c r="R5" t="n">
-        <v>7036003</v>
+        <v>7035839</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,69 +1075,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166473</t>
+          <t>https://artportalen.se/Sighting/135978185</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105166457</v>
+        <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>80412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Larsmyran, Larsmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601301</v>
+        <v>601386</v>
       </c>
       <c r="R6" t="n">
-        <v>7035773</v>
+        <v>7035851</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1160,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,31 +1181,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166457</t>
+          <t>https://artportalen.se/Sighting/135915394</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105166462</v>
+        <v>105166448</v>
       </c>
       <c r="B7" t="n">
-        <v>91930</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601281</v>
+        <v>601307</v>
       </c>
       <c r="R7" t="n">
-        <v>7035861</v>
+        <v>7035771</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,16 +1298,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166462</t>
+          <t>https://artportalen.se/Sighting/105166448</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105166465</v>
+        <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,37 +1315,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601338</v>
+        <v>601407</v>
       </c>
       <c r="R8" t="n">
-        <v>7035915</v>
+        <v>7035824</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,12 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,53 +1389,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166465</t>
+          <t>https://artportalen.se/Sighting/135978170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105166445</v>
+        <v>105166442</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>81312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601318</v>
+        <v>601315</v>
       </c>
       <c r="R9" t="n">
-        <v>7035735</v>
+        <v>7035729</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,54 +1506,54 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166445</t>
+          <t>https://artportalen.se/Sighting/105166442</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105166454</v>
+        <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601302</v>
+        <v>601395</v>
       </c>
       <c r="R10" t="n">
-        <v>7035775</v>
+        <v>7035891</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,12 +1577,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,31 +1597,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166454</t>
+          <t>https://artportalen.se/Sighting/135978163</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105166469</v>
+        <v>105166473</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601360</v>
+        <v>601383</v>
       </c>
       <c r="R11" t="n">
-        <v>7035964</v>
+        <v>7036003</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,54 +1714,54 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166469</t>
+          <t>https://artportalen.se/Sighting/105166473</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105166460</v>
+        <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>80468</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601299</v>
+        <v>601232</v>
       </c>
       <c r="R12" t="n">
-        <v>7035779</v>
+        <v>7035614</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,12 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,75 +1799,72 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166460</t>
+          <t>https://artportalen.se/Sighting/135978176</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105166451</v>
+        <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Backsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601304</v>
+        <v>601264</v>
       </c>
       <c r="R13" t="n">
-        <v>7035772</v>
+        <v>7035494</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,12 +1888,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,53 +1908,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166451</t>
+          <t>https://artportalen.se/Sighting/135978186</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105166429</v>
+        <v>105166457</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>91966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601387</v>
+        <v>601301</v>
       </c>
       <c r="R14" t="n">
-        <v>7035763</v>
+        <v>7035773</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2032,6 +2004,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2053,38 +2026,38 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105166429</t>
+          <t>https://artportalen.se/Sighting/105166457</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105166439</v>
+        <v>105166462</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601258</v>
+        <v>601281</v>
       </c>
       <c r="R15" t="n">
-        <v>7035788</v>
+        <v>7035861</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2132,11 +2105,6 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett trettiotal</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2164,7 +2132,4814 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/105166462</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105166465</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601338</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7035915</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166465</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135915210</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92071</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7035835</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135978168</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92071</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>601345</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7035914</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978168</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135978169</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92071</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>601343</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7035913</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978169</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135914668</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92013</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>601323</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7035796</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914668</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>105166445</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>601318</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7035735</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166445</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105166454</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>601302</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7035775</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166454</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135913946</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>601368</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7035698</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135913946</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135914277</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>601361</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7035764</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914277</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135914470</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>601355</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7035750</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914470</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135914629</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>601328</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7035785</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914629</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135915117</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>601383</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7035805</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915117</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135978181</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>601288</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7035786</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978181</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135978182</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>601345</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7035926</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978182</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135978183</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>601409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7035870</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978183</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135914132</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>601385</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7035714</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914132</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135978190</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>601379</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7035913</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978190</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135914710</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83411</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>601335</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7035805</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914710</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135915780</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7035848</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915780</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135978177</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>601347</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7035924</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978177</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>105166469</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>601360</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7035964</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166469</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135978162</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>601409</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7035872</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978162</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135914541</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>601345</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7035773</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914541</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135915235</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7035832</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915235</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135978172</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>601254</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7035779</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978172</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135978173</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>601319</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7035834</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978173</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135978174</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>601324</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7035838</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978174</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135978175</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>601334</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7035845</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978175</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>105166460</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>601299</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7035779</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166460</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135914002</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>601372</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7035745</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914002</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135978164</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>601281</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7035786</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978164</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135978166</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>601290</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7035813</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978166</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135978167</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>601418</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7035888</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978167</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>105166451</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>601304</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7035772</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166451</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>105166429</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>601387</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7035763</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105166429</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135914304</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>601359</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7035757</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914304</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>105166439</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>601258</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7035788</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-10-13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ett trettiotal</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/105166439</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135914183</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>601394</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7035731</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914183</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135914883</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>601345</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7035812</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914883</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135915086</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>601365</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7035799</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915086</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135915150</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7035813</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915150</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135978178</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>601254</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7035779</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978178</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135978179</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>601417</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7035846</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978179</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135978180</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Backsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>601415</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7035834</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135978180</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135915267</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80506</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>601384</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7035832</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135915267</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135914240</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Larsmyran, Larsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>601354</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7035765</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135914240</t>
         </is>
       </c>
     </row>
@@ -2184,6 +6959,52 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80412</v>
+        <v>80414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83411</v>
+        <v>83413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58817</v>
+        <v>58819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80414</v>
+        <v>80415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83413</v>
+        <v>83414</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80415</v>
+        <v>80416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80416</v>
+        <v>80420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80420</v>
+        <v>80421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83419</v>
+        <v>83420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80421</v>
+        <v>80425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83420</v>
+        <v>83424</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80425</v>
+        <v>80431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83424</v>
+        <v>83430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83439</v>
+        <v>83452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80431</v>
+        <v>80444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83430</v>
+        <v>83443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>135914002</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>135978164</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>135978166</v>
       </c>
       <c r="B47" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>135978167</v>
       </c>
       <c r="B48" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>135914304</v>
       </c>
       <c r="B51" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 5310-2024 artfynd.xlsx
+++ b/artfynd/A 5310-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135978189</v>
       </c>
       <c r="B2" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135978184</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135978185</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135915394</v>
       </c>
       <c r="B6" t="n">
-        <v>80444</v>
+        <v>80445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>135978170</v>
       </c>
       <c r="B8" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>135978163</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135978176</v>
       </c>
       <c r="B12" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>135978186</v>
       </c>
       <c r="B13" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135915210</v>
       </c>
       <c r="B17" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>135978168</v>
       </c>
       <c r="B18" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>135978169</v>
       </c>
       <c r="B19" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>135914668</v>
       </c>
       <c r="B20" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>135913946</v>
       </c>
       <c r="B23" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>135914277</v>
       </c>
       <c r="B24" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>135914470</v>
       </c>
       <c r="B25" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>135914629</v>
       </c>
       <c r="B26" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>135915117</v>
       </c>
       <c r="B27" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>135978181</v>
       </c>
       <c r="B28" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135978182</v>
       </c>
       <c r="B29" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>135978183</v>
       </c>
       <c r="B30" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>135914132</v>
       </c>
       <c r="B31" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>135978190</v>
       </c>
       <c r="B32" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>135914710</v>
       </c>
       <c r="B33" t="n">
-        <v>83443</v>
+        <v>83444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>135915780</v>
       </c>
       <c r="B34" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>135978177</v>
       </c>
       <c r="B35" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>135978162</v>
       </c>
       <c r="B37" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135914541</v>
       </c>
       <c r="B38" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135915235</v>
       </c>
       <c r="B39" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135978172</v>
       </c>
       <c r="B40" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>135978173</v>
       </c>
       <c r="B41" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135978174</v>
       </c>
       <c r="B42" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>135978175</v>
       </c>
       <c r="B43" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>135914183</v>
       </c>
       <c r="B53" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>135914883</v>
       </c>
       <c r="B54" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135915086</v>
       </c>
       <c r="B55" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>135915150</v>
       </c>
       <c r="B56" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>135978178</v>
       </c>
       <c r="B57" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>135978179</v>
       </c>
       <c r="B58" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>135978180</v>
       </c>
       <c r="B59" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>135915267</v>
       </c>
       <c r="B60" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>135914240</v>
       </c>
       <c r="B61" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
